--- a/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CULTURAL Y DEPORTIVA LEONESA.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CULTURAL Y DEPORTIVA LEONESA.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P. ORENGA IMAZ</t>
+          <t>A. DOMINGUEZ ESPELT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,70 +562,70 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>16.7191</v>
+        <v>17.9987</v>
       </c>
       <c r="E2" t="n">
-        <v>24.4963</v>
+        <v>18.3249</v>
       </c>
       <c r="F2" t="n">
-        <v>-7.7774</v>
+        <v>-0.3260999999999998</v>
       </c>
       <c r="G2" t="n">
-        <v>7.6435</v>
+        <v>15.8519</v>
       </c>
       <c r="H2" t="n">
-        <v>4.4389</v>
+        <v>3.208799999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>3.2044</v>
+        <v>12.643</v>
       </c>
       <c r="J2" t="n">
-        <v>14.2992</v>
+        <v>29.4769</v>
       </c>
       <c r="K2" t="n">
-        <v>8.420999999999999</v>
+        <v>12.5641</v>
       </c>
       <c r="L2" t="n">
-        <v>5.8784</v>
+        <v>16.9128</v>
       </c>
       <c r="M2" t="n">
-        <v>-6.6557</v>
+        <v>-13.6253</v>
       </c>
       <c r="N2" t="n">
-        <v>-3.982</v>
+        <v>-9.355600000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.6737</v>
+        <v>-4.2698</v>
       </c>
       <c r="P2" t="n">
-        <v>9.157</v>
+        <v>-5.6191</v>
       </c>
       <c r="Q2" t="n">
-        <v>-5.202999999999999</v>
+        <v>-24.5581</v>
       </c>
       <c r="R2" t="n">
-        <v>14.36</v>
+        <v>18.9388</v>
       </c>
       <c r="S2" t="n">
-        <v>11.4626</v>
+        <v>-2.5966</v>
       </c>
       <c r="T2" t="n">
-        <v>12.0214</v>
+        <v>-0.7813999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5587000000000001</v>
+        <v>-1.8152</v>
       </c>
       <c r="V2" t="n">
-        <v>-11.5444</v>
+        <v>10.3625</v>
       </c>
       <c r="W2" t="n">
-        <v>3.3788</v>
+        <v>14.1872</v>
       </c>
       <c r="X2" t="n">
-        <v>-14.923</v>
+        <v>-3.8246</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>10.16</v>
+        <v>17.8291</v>
       </c>
       <c r="E3" t="n">
-        <v>24.4665</v>
+        <v>25.8692</v>
       </c>
       <c r="F3" t="n">
-        <v>-14.3073</v>
+        <v>-8.039999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>1.8364</v>
@@ -688,13 +688,13 @@
         <v>44.537</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.7745</v>
+        <v>4.8957</v>
       </c>
       <c r="T3" t="n">
-        <v>2.9962</v>
+        <v>4.398999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>-5.7705</v>
+        <v>0.4965999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>-1.182</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. DOMINGUEZ ESPELT</t>
+          <t>D. CEBOLLA PORCAR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>6.1865</v>
+        <v>12.7783</v>
       </c>
       <c r="E4" t="n">
-        <v>10.1762</v>
+        <v>11.5972</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.99</v>
+        <v>1.181</v>
       </c>
       <c r="G4" t="n">
-        <v>15.8519</v>
+        <v>11.0393</v>
       </c>
       <c r="H4" t="n">
-        <v>3.208799999999999</v>
+        <v>0.5095999999999994</v>
       </c>
       <c r="I4" t="n">
-        <v>12.643</v>
+        <v>10.5297</v>
       </c>
       <c r="J4" t="n">
-        <v>29.4769</v>
+        <v>37.8721</v>
       </c>
       <c r="K4" t="n">
-        <v>12.5641</v>
+        <v>10.7246</v>
       </c>
       <c r="L4" t="n">
-        <v>16.9128</v>
+        <v>27.1473</v>
       </c>
       <c r="M4" t="n">
-        <v>-13.6253</v>
+        <v>-26.833</v>
       </c>
       <c r="N4" t="n">
-        <v>-9.355600000000001</v>
+        <v>-10.2152</v>
       </c>
       <c r="O4" t="n">
-        <v>-4.2698</v>
+        <v>-16.6181</v>
       </c>
       <c r="P4" t="n">
-        <v>-5.6191</v>
+        <v>-7.284199999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>-24.5581</v>
+        <v>-49.3243</v>
       </c>
       <c r="R4" t="n">
-        <v>18.9388</v>
+        <v>42.0399</v>
       </c>
       <c r="S4" t="n">
-        <v>-14.4093</v>
+        <v>-0.6670999999999998</v>
       </c>
       <c r="T4" t="n">
-        <v>-8.93</v>
+        <v>-0.7081999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>-5.4789</v>
+        <v>0.04089999999999983</v>
       </c>
       <c r="V4" t="n">
-        <v>10.3625</v>
+        <v>9.6904</v>
       </c>
       <c r="W4" t="n">
-        <v>14.1872</v>
+        <v>23.7574</v>
       </c>
       <c r="X4" t="n">
-        <v>-3.8246</v>
+        <v>-14.0671</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. GONZALEZ CORDERO</t>
+          <t>P. ORENGA IMAZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>3.2805</v>
+        <v>10.4901</v>
       </c>
       <c r="E5" t="n">
-        <v>4.4258</v>
+        <v>17.6197</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.145</v>
+        <v>-7.1295</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7628999999999999</v>
+        <v>7.6435</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8317</v>
+        <v>4.4389</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.0689</v>
+        <v>3.2044</v>
       </c>
       <c r="J5" t="n">
-        <v>4.6375</v>
+        <v>14.2992</v>
       </c>
       <c r="K5" t="n">
-        <v>4.2938</v>
+        <v>8.420999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3438</v>
+        <v>5.8784</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.8744</v>
+        <v>-6.6557</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.462</v>
+        <v>-3.982</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.4126</v>
+        <v>-2.6737</v>
       </c>
       <c r="P5" t="n">
-        <v>3.1217</v>
+        <v>9.157</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.0812</v>
+        <v>-5.202999999999999</v>
       </c>
       <c r="R5" t="n">
-        <v>5.2029</v>
+        <v>14.36</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1293</v>
+        <v>5.234</v>
       </c>
       <c r="T5" t="n">
-        <v>1.6393</v>
+        <v>5.1447</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.51</v>
+        <v>0.08929999999999988</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.7335</v>
+        <v>-11.5444</v>
       </c>
       <c r="W5" t="n">
-        <v>0.23</v>
+        <v>3.3788</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.9635</v>
+        <v>-14.923</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. TRAORE</t>
+          <t>A. GONZALEZ CORDERO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>1.937600000000001</v>
+        <v>3.4542</v>
       </c>
       <c r="E6" t="n">
-        <v>16.5548</v>
+        <v>3.6755</v>
       </c>
       <c r="F6" t="n">
-        <v>-14.6172</v>
+        <v>-0.2213000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>-4.418900000000001</v>
+        <v>0.7628999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>7.6325</v>
+        <v>2.8317</v>
       </c>
       <c r="I6" t="n">
-        <v>-12.0511</v>
+        <v>-2.0689</v>
       </c>
       <c r="J6" t="n">
-        <v>20.6203</v>
+        <v>4.6375</v>
       </c>
       <c r="K6" t="n">
-        <v>15.6247</v>
+        <v>4.2938</v>
       </c>
       <c r="L6" t="n">
-        <v>4.9956</v>
+        <v>0.3438</v>
       </c>
       <c r="M6" t="n">
-        <v>-25.0391</v>
+        <v>-3.8744</v>
       </c>
       <c r="N6" t="n">
-        <v>-7.9924</v>
+        <v>-1.462</v>
       </c>
       <c r="O6" t="n">
-        <v>-17.0468</v>
+        <v>-2.4126</v>
       </c>
       <c r="P6" t="n">
-        <v>-12.9033</v>
+        <v>3.1217</v>
       </c>
       <c r="Q6" t="n">
-        <v>-38.71</v>
+        <v>-2.0812</v>
       </c>
       <c r="R6" t="n">
-        <v>25.8067</v>
+        <v>5.2029</v>
       </c>
       <c r="S6" t="n">
-        <v>20.7739</v>
+        <v>1.3031</v>
       </c>
       <c r="T6" t="n">
-        <v>14.4072</v>
+        <v>0.8892999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>6.3666</v>
+        <v>0.4138000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.5143</v>
+        <v>-1.7335</v>
       </c>
       <c r="W6" t="n">
-        <v>20.2372</v>
+        <v>0.23</v>
       </c>
       <c r="X6" t="n">
-        <v>-21.7512</v>
+        <v>-1.9635</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. LLAMAS PRADO</t>
+          <t>M. DENG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2861999999999991</v>
+        <v>2.9695</v>
       </c>
       <c r="E7" t="n">
-        <v>5.4879</v>
+        <v>16.1408</v>
       </c>
       <c r="F7" t="n">
-        <v>-5.2019</v>
+        <v>-13.1713</v>
       </c>
       <c r="G7" t="n">
-        <v>-16.2639</v>
+        <v>-8.630099999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>-4.664099999999999</v>
+        <v>-10.6487</v>
       </c>
       <c r="I7" t="n">
-        <v>-11.5997</v>
+        <v>2.018900000000002</v>
       </c>
       <c r="J7" t="n">
-        <v>12.6628</v>
+        <v>22.1017</v>
       </c>
       <c r="K7" t="n">
-        <v>8.942600000000001</v>
+        <v>6.167400000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>3.7199</v>
+        <v>15.9342</v>
       </c>
       <c r="M7" t="n">
-        <v>-28.9264</v>
+        <v>-30.732</v>
       </c>
       <c r="N7" t="n">
-        <v>-13.6068</v>
+        <v>-16.8165</v>
       </c>
       <c r="O7" t="n">
-        <v>-15.3199</v>
+        <v>-13.9157</v>
       </c>
       <c r="P7" t="n">
-        <v>11.2384</v>
+        <v>10.6142</v>
       </c>
       <c r="Q7" t="n">
-        <v>-22.4768</v>
+        <v>-31.0097</v>
       </c>
       <c r="R7" t="n">
-        <v>33.7151</v>
+        <v>41.6237</v>
       </c>
       <c r="S7" t="n">
-        <v>4.1866</v>
+        <v>-3.6879</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8660999999999999</v>
+        <v>0.3541999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>5.0528</v>
+        <v>-4.0418</v>
       </c>
       <c r="V7" t="n">
-        <v>1.1249</v>
+        <v>4.673699999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>16.1684</v>
+        <v>24.6953</v>
       </c>
       <c r="X7" t="n">
-        <v>-15.0436</v>
+        <v>-20.0214</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Y. IGLESIAS MENDEZ</t>
+          <t>J. LLAMAS PRADO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1424</v>
+        <v>1.146199999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0069</v>
+        <v>7.599</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1492</v>
+        <v>-6.4529</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1032</v>
+        <v>-16.2639</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0788</v>
+        <v>-4.664099999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1821</v>
+        <v>-11.5997</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0584</v>
+        <v>12.6628</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0192</v>
+        <v>8.942600000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0392</v>
+        <v>3.7199</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0449</v>
+        <v>-28.9264</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.098</v>
+        <v>-13.6068</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1429</v>
+        <v>-15.3199</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2081</v>
+        <v>11.2384</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-22.4768</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2081</v>
+        <v>33.7151</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.169</v>
+        <v>5.0463</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.06519999999999999</v>
+        <v>1.2444</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1037</v>
+        <v>3.8022</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.1249</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>16.1684</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-15.0436</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. CEBOLLA PORCAR</t>
+          <t>Y. IGLESIAS MENDEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,70 +1108,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.06859999999999911</v>
+        <v>0.2011</v>
       </c>
       <c r="E9" t="n">
-        <v>4.105500000000001</v>
+        <v>-0.0069</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.037000000000001</v>
+        <v>0.208</v>
       </c>
       <c r="G9" t="n">
-        <v>11.0393</v>
+        <v>0.1032</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5095999999999994</v>
+        <v>-0.0788</v>
       </c>
       <c r="I9" t="n">
-        <v>10.5297</v>
+        <v>0.1821</v>
       </c>
       <c r="J9" t="n">
-        <v>37.8721</v>
+        <v>0.0584</v>
       </c>
       <c r="K9" t="n">
-        <v>10.7246</v>
+        <v>0.0192</v>
       </c>
       <c r="L9" t="n">
-        <v>27.1473</v>
+        <v>0.0392</v>
       </c>
       <c r="M9" t="n">
-        <v>-26.833</v>
+        <v>0.0449</v>
       </c>
       <c r="N9" t="n">
-        <v>-10.2152</v>
+        <v>-0.098</v>
       </c>
       <c r="O9" t="n">
-        <v>-16.6181</v>
+        <v>0.1429</v>
       </c>
       <c r="P9" t="n">
-        <v>-7.284199999999999</v>
+        <v>0.2081</v>
       </c>
       <c r="Q9" t="n">
-        <v>-49.3243</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>42.0399</v>
+        <v>0.2081</v>
       </c>
       <c r="S9" t="n">
-        <v>-13.3768</v>
+        <v>-0.1103</v>
       </c>
       <c r="T9" t="n">
-        <v>-8.1999</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>-5.176699999999999</v>
+        <v>-0.045</v>
       </c>
       <c r="V9" t="n">
-        <v>9.6904</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>23.7574</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-14.0671</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.469099999999999</v>
+        <v>-4.924200000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.4641</v>
+        <v>-3.3691</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.005</v>
+        <v>-1.5549</v>
       </c>
       <c r="G10" t="n">
         <v>-1.5528</v>
@@ -1234,13 +1234,13 @@
         <v>8.1166</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3334000000000002</v>
+        <v>1.8784</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2684000000000002</v>
+        <v>0.8266</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6019</v>
+        <v>1.0519</v>
       </c>
       <c r="V10" t="n">
         <v>-1.5037</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. DENG</t>
+          <t>A. TRAORE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D11" t="n">
-        <v>-11.0215</v>
+        <v>-9.3347</v>
       </c>
       <c r="E11" t="n">
-        <v>8.7142</v>
+        <v>6.789700000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-19.7359</v>
+        <v>-16.1245</v>
       </c>
       <c r="G11" t="n">
-        <v>-8.630099999999999</v>
+        <v>-4.418900000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>-10.6487</v>
+        <v>7.6325</v>
       </c>
       <c r="I11" t="n">
-        <v>2.018900000000002</v>
+        <v>-12.0511</v>
       </c>
       <c r="J11" t="n">
-        <v>22.1017</v>
+        <v>20.6203</v>
       </c>
       <c r="K11" t="n">
-        <v>6.167400000000001</v>
+        <v>15.6247</v>
       </c>
       <c r="L11" t="n">
-        <v>15.9342</v>
+        <v>4.9956</v>
       </c>
       <c r="M11" t="n">
-        <v>-30.732</v>
+        <v>-25.0391</v>
       </c>
       <c r="N11" t="n">
-        <v>-16.8165</v>
+        <v>-7.9924</v>
       </c>
       <c r="O11" t="n">
-        <v>-13.9157</v>
+        <v>-17.0468</v>
       </c>
       <c r="P11" t="n">
-        <v>10.6142</v>
+        <v>-12.9033</v>
       </c>
       <c r="Q11" t="n">
-        <v>-31.0097</v>
+        <v>-38.71</v>
       </c>
       <c r="R11" t="n">
-        <v>41.6237</v>
+        <v>25.8067</v>
       </c>
       <c r="S11" t="n">
-        <v>-17.6793</v>
+        <v>9.5014</v>
       </c>
       <c r="T11" t="n">
-        <v>-7.0727</v>
+        <v>4.6424</v>
       </c>
       <c r="U11" t="n">
-        <v>-10.6064</v>
+        <v>4.8594</v>
       </c>
       <c r="V11" t="n">
-        <v>4.673699999999999</v>
+        <v>-1.5143</v>
       </c>
       <c r="W11" t="n">
-        <v>24.6953</v>
+        <v>20.2372</v>
       </c>
       <c r="X11" t="n">
-        <v>-20.0214</v>
+        <v>-21.7512</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>E. VAN DER HEIJDEN</t>
+          <t>R. LLAMAS MARTINEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>26</v>
       </c>
       <c r="D12" t="n">
-        <v>-13.14</v>
+        <v>-9.507899999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.232899999999999</v>
+        <v>-4.4934</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.907300000000001</v>
+        <v>-5.0143</v>
       </c>
       <c r="G12" t="n">
-        <v>-21.8735</v>
+        <v>-24.3469</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5947000000000009</v>
+        <v>-4.3544</v>
       </c>
       <c r="I12" t="n">
-        <v>-21.2792</v>
+        <v>-19.9925</v>
       </c>
       <c r="J12" t="n">
-        <v>20.4608</v>
+        <v>3.5063</v>
       </c>
       <c r="K12" t="n">
-        <v>16.2923</v>
+        <v>9.635999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>4.1686</v>
+        <v>-6.1299</v>
       </c>
       <c r="M12" t="n">
-        <v>-42.3343</v>
+        <v>-27.8531</v>
       </c>
       <c r="N12" t="n">
-        <v>-16.8868</v>
+        <v>-13.9906</v>
       </c>
       <c r="O12" t="n">
-        <v>-25.4477</v>
+        <v>-13.8625</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.8729</v>
+        <v>12.2792</v>
       </c>
       <c r="Q12" t="n">
-        <v>-53.0703</v>
+        <v>-20.6038</v>
       </c>
       <c r="R12" t="n">
-        <v>51.1972</v>
+        <v>32.8828</v>
       </c>
       <c r="S12" t="n">
-        <v>10.6878</v>
+        <v>-0.06849999999999995</v>
       </c>
       <c r="T12" t="n">
-        <v>7.9779</v>
+        <v>-2.1671</v>
       </c>
       <c r="U12" t="n">
-        <v>2.7097</v>
+        <v>2.0983</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.08140000000000036</v>
+        <v>2.6287</v>
       </c>
       <c r="W12" t="n">
-        <v>16.3987</v>
+        <v>14.7709</v>
       </c>
       <c r="X12" t="n">
-        <v>-16.4797</v>
+        <v>-12.1423</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R. LLAMAS MARTINEZ</t>
+          <t>G. MCKAY JR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D13" t="n">
-        <v>-14.2246</v>
+        <v>-12.203</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.419700000000001</v>
+        <v>-16.2592</v>
       </c>
       <c r="F13" t="n">
-        <v>-6.8052</v>
+        <v>4.056</v>
       </c>
       <c r="G13" t="n">
-        <v>-24.3469</v>
+        <v>-13.715</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.3544</v>
+        <v>-13.9559</v>
       </c>
       <c r="I13" t="n">
-        <v>-19.9925</v>
+        <v>0.2407999999999993</v>
       </c>
       <c r="J13" t="n">
-        <v>3.5063</v>
+        <v>-2.8535</v>
       </c>
       <c r="K13" t="n">
-        <v>9.635999999999999</v>
+        <v>-7.0297</v>
       </c>
       <c r="L13" t="n">
-        <v>-6.1299</v>
+        <v>4.175800000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-27.8531</v>
+        <v>-10.8617</v>
       </c>
       <c r="N13" t="n">
-        <v>-13.9906</v>
+        <v>-6.9266</v>
       </c>
       <c r="O13" t="n">
-        <v>-13.8625</v>
+        <v>-3.9351</v>
       </c>
       <c r="P13" t="n">
-        <v>12.2792</v>
+        <v>8.3249</v>
       </c>
       <c r="Q13" t="n">
-        <v>-20.6038</v>
+        <v>-17.8983</v>
       </c>
       <c r="R13" t="n">
-        <v>32.8828</v>
+        <v>26.2229</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.7854</v>
+        <v>-0.4656000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-5.0932</v>
+        <v>-2.495</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3076999999999998</v>
+        <v>2.029</v>
       </c>
       <c r="V13" t="n">
-        <v>2.6287</v>
+        <v>-6.347300000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>14.7709</v>
+        <v>6.9877</v>
       </c>
       <c r="X13" t="n">
-        <v>-12.1423</v>
+        <v>-13.3347</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. MCKAY JR</t>
+          <t>D. BULTO CASTILLO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>24</v>
       </c>
       <c r="D14" t="n">
-        <v>-15.2668</v>
+        <v>-14.1582</v>
       </c>
       <c r="E14" t="n">
-        <v>-18.4302</v>
+        <v>-8.631599999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>3.1634</v>
+        <v>-5.5267</v>
       </c>
       <c r="G14" t="n">
-        <v>-13.715</v>
+        <v>-9.650500000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>-13.9559</v>
+        <v>-6.593699999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2407999999999993</v>
+        <v>-3.0567</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.8535</v>
+        <v>8.2524</v>
       </c>
       <c r="K14" t="n">
-        <v>-7.0297</v>
+        <v>2.4064</v>
       </c>
       <c r="L14" t="n">
-        <v>4.175800000000001</v>
+        <v>5.846299999999998</v>
       </c>
       <c r="M14" t="n">
-        <v>-10.8617</v>
+        <v>-17.9029</v>
       </c>
       <c r="N14" t="n">
-        <v>-6.9266</v>
+        <v>-9.0001</v>
       </c>
       <c r="O14" t="n">
-        <v>-3.9351</v>
+        <v>-8.9026</v>
       </c>
       <c r="P14" t="n">
-        <v>8.3249</v>
+        <v>8.1165</v>
       </c>
       <c r="Q14" t="n">
-        <v>-17.8983</v>
+        <v>-13.7359</v>
       </c>
       <c r="R14" t="n">
-        <v>26.2229</v>
+        <v>21.8524</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.529399999999999</v>
+        <v>0.6181999999999997</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.6662</v>
+        <v>-1.8391</v>
       </c>
       <c r="U14" t="n">
-        <v>1.1369</v>
+        <v>2.4577</v>
       </c>
       <c r="V14" t="n">
-        <v>-6.347300000000001</v>
+        <v>-13.2426</v>
       </c>
       <c r="W14" t="n">
-        <v>6.9877</v>
+        <v>-1.309</v>
       </c>
       <c r="X14" t="n">
-        <v>-13.3347</v>
+        <v>-11.9335</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. BULTO CASTILLO</t>
+          <t>E. VAN DER HEIJDEN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,70 +1576,70 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>-17.6013</v>
+        <v>-14.4155</v>
       </c>
       <c r="E15" t="n">
-        <v>-10.8029</v>
+        <v>-9.979800000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>-6.798900000000001</v>
+        <v>-4.435700000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>-9.650500000000001</v>
+        <v>-21.8735</v>
       </c>
       <c r="H15" t="n">
-        <v>-6.593699999999999</v>
+        <v>-0.5947000000000009</v>
       </c>
       <c r="I15" t="n">
-        <v>-3.0567</v>
+        <v>-21.2792</v>
       </c>
       <c r="J15" t="n">
-        <v>8.2524</v>
+        <v>20.4608</v>
       </c>
       <c r="K15" t="n">
-        <v>2.4064</v>
+        <v>16.2923</v>
       </c>
       <c r="L15" t="n">
-        <v>5.846299999999998</v>
+        <v>4.1686</v>
       </c>
       <c r="M15" t="n">
-        <v>-17.9029</v>
+        <v>-42.3343</v>
       </c>
       <c r="N15" t="n">
-        <v>-9.0001</v>
+        <v>-16.8868</v>
       </c>
       <c r="O15" t="n">
-        <v>-8.9026</v>
+        <v>-25.4477</v>
       </c>
       <c r="P15" t="n">
-        <v>8.1165</v>
+        <v>-1.8729</v>
       </c>
       <c r="Q15" t="n">
-        <v>-13.7359</v>
+        <v>-53.0703</v>
       </c>
       <c r="R15" t="n">
-        <v>21.8524</v>
+        <v>51.1972</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.8249</v>
+        <v>9.4123</v>
       </c>
       <c r="T15" t="n">
-        <v>-4.0105</v>
+        <v>6.2309</v>
       </c>
       <c r="U15" t="n">
-        <v>1.1853</v>
+        <v>3.1814</v>
       </c>
       <c r="V15" t="n">
-        <v>-13.2426</v>
+        <v>-0.08140000000000036</v>
       </c>
       <c r="W15" t="n">
-        <v>-1.309</v>
+        <v>16.3987</v>
       </c>
       <c r="X15" t="n">
-        <v>-11.9335</v>
+        <v>-16.4797</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>20</v>
       </c>
       <c r="D16" t="n">
-        <v>-18.4903</v>
+        <v>-28.681</v>
       </c>
       <c r="E16" t="n">
-        <v>-4.813200000000001</v>
+        <v>-13.1154</v>
       </c>
       <c r="F16" t="n">
-        <v>-13.6769</v>
+        <v>-15.5658</v>
       </c>
       <c r="G16" t="n">
         <v>-25.8927</v>
@@ -1702,13 +1702,13 @@
         <v>24.5579</v>
       </c>
       <c r="S16" t="n">
-        <v>15.3972</v>
+        <v>5.2065</v>
       </c>
       <c r="T16" t="n">
-        <v>11.4657</v>
+        <v>3.1634</v>
       </c>
       <c r="U16" t="n">
-        <v>3.9318</v>
+        <v>2.043</v>
       </c>
       <c r="V16" t="n">
         <v>-8.8271</v>
@@ -1735,13 +1735,13 @@
         <v>26</v>
       </c>
       <c r="D17" t="n">
-        <v>-57.4327</v>
+        <v>-26.3573</v>
       </c>
       <c r="E17" t="n">
-        <v>44.2573</v>
+        <v>51.76060000000002</v>
       </c>
       <c r="F17" t="n">
-        <v>-101.6924</v>
+        <v>-78.11799999999999</v>
       </c>
       <c r="G17" t="n">
         <v>-89.1071</v>
@@ -1750,7 +1750,7 @@
         <v>-34.6523</v>
       </c>
       <c r="I17" t="n">
-        <v>-54.45519999999999</v>
+        <v>-54.4552</v>
       </c>
       <c r="J17" t="n">
         <v>208.1662</v>
@@ -1759,7 +1759,7 @@
         <v>112.5654</v>
       </c>
       <c r="L17" t="n">
-        <v>95.601</v>
+        <v>95.60099999999998</v>
       </c>
       <c r="M17" t="n">
         <v>-297.2735</v>
@@ -1780,13 +1780,13 @@
         <v>391.262</v>
       </c>
       <c r="S17" t="n">
-        <v>4.422200000000002</v>
+        <v>35.4999</v>
       </c>
       <c r="T17" t="n">
-        <v>11.3355</v>
+        <v>18.8389</v>
       </c>
       <c r="U17" t="n">
-        <v>-6.912200000000001</v>
+        <v>16.6615</v>
       </c>
       <c r="V17" t="n">
         <v>-17.4961</v>
